--- a/diseases/d096/2005-2009.xlsx
+++ b/diseases/d096/2005-2009.xlsx
@@ -913,9 +913,6 @@
       <c r="O3" t="n">
         <v>2</v>
       </c>
-      <c r="Q3" t="n">
-        <v>0</v>
-      </c>
       <c r="R3" t="n">
         <v>0.03812368925990863</v>
       </c>
@@ -1457,9 +1454,6 @@
       <c r="O6" t="n">
         <v>2</v>
       </c>
-      <c r="Q6" t="n">
-        <v>0</v>
-      </c>
       <c r="R6" t="n">
         <v>0.03812368925990863</v>
       </c>
@@ -2001,9 +1995,6 @@
       <c r="O9" t="n">
         <v>0</v>
       </c>
-      <c r="Q9" t="n">
-        <v>0</v>
-      </c>
       <c r="R9" t="n">
         <v>0</v>
       </c>
@@ -2545,9 +2536,6 @@
       <c r="O12" t="n">
         <v>2</v>
       </c>
-      <c r="Q12" t="n">
-        <v>0</v>
-      </c>
       <c r="R12" t="n">
         <v>0.03812368925990863</v>
       </c>
@@ -3089,9 +3077,6 @@
       <c r="O15" t="n">
         <v>0</v>
       </c>
-      <c r="Q15" t="n">
-        <v>0</v>
-      </c>
       <c r="R15" t="n">
         <v>0</v>
       </c>
@@ -3633,9 +3618,6 @@
       <c r="O18" t="n">
         <v>0</v>
       </c>
-      <c r="Q18" t="n">
-        <v>0</v>
-      </c>
       <c r="R18" t="n">
         <v>0</v>
       </c>
@@ -4177,9 +4159,6 @@
       <c r="O21" t="n">
         <v>2</v>
       </c>
-      <c r="Q21" t="n">
-        <v>0</v>
-      </c>
       <c r="R21" t="n">
         <v>0.03812368925990863</v>
       </c>
@@ -4721,9 +4700,6 @@
       <c r="O24" t="n">
         <v>3</v>
       </c>
-      <c r="Q24" t="n">
-        <v>0</v>
-      </c>
       <c r="R24" t="n">
         <v>0.05718553388986295</v>
       </c>
@@ -5265,9 +5241,6 @@
       <c r="O27" t="n">
         <v>0</v>
       </c>
-      <c r="Q27" t="n">
-        <v>0</v>
-      </c>
       <c r="R27" t="n">
         <v>0</v>
       </c>
@@ -5809,9 +5782,6 @@
       <c r="O30" t="n">
         <v>3</v>
       </c>
-      <c r="Q30" t="n">
-        <v>0</v>
-      </c>
       <c r="R30" t="n">
         <v>0.05718553388986295</v>
       </c>
@@ -6353,9 +6323,6 @@
       <c r="O33" t="n">
         <v>0</v>
       </c>
-      <c r="Q33" t="n">
-        <v>0</v>
-      </c>
       <c r="R33" t="n">
         <v>0</v>
       </c>
@@ -6897,9 +6864,6 @@
       <c r="O36" t="n">
         <v>0</v>
       </c>
-      <c r="Q36" t="n">
-        <v>0</v>
-      </c>
       <c r="R36" t="n">
         <v>0</v>
       </c>
@@ -7441,9 +7405,6 @@
       <c r="O39" t="n">
         <v>2</v>
       </c>
-      <c r="Q39" t="n">
-        <v>0</v>
-      </c>
       <c r="R39" t="n">
         <v>0.03797771334858708</v>
       </c>
@@ -8577,9 +8538,6 @@
       <c r="O46" t="n">
         <v>1</v>
       </c>
-      <c r="Q46" t="n">
-        <v>0</v>
-      </c>
       <c r="R46" t="n">
         <v>0.01898885667429354</v>
       </c>
@@ -9713,9 +9671,6 @@
       <c r="O53" t="n">
         <v>1</v>
       </c>
-      <c r="Q53" t="n">
-        <v>0</v>
-      </c>
       <c r="R53" t="n">
         <v>0.01898885667429354</v>
       </c>
@@ -10849,9 +10804,6 @@
       <c r="O60" t="n">
         <v>0</v>
       </c>
-      <c r="Q60" t="n">
-        <v>0</v>
-      </c>
       <c r="R60" t="n">
         <v>0</v>
       </c>
@@ -12133,9 +12085,6 @@
       <c r="O68" t="n">
         <v>0</v>
       </c>
-      <c r="Q68" t="n">
-        <v>0</v>
-      </c>
       <c r="R68" t="n">
         <v>0</v>
       </c>
@@ -13269,9 +13218,6 @@
       <c r="O75" t="n">
         <v>1</v>
       </c>
-      <c r="Q75" t="n">
-        <v>0</v>
-      </c>
       <c r="R75" t="n">
         <v>0.01898885667429354</v>
       </c>
@@ -14405,9 +14351,6 @@
       <c r="O82" t="n">
         <v>0</v>
       </c>
-      <c r="Q82" t="n">
-        <v>0</v>
-      </c>
       <c r="R82" t="n">
         <v>0</v>
       </c>
@@ -15689,9 +15632,6 @@
       <c r="O90" t="n">
         <v>0</v>
       </c>
-      <c r="Q90" t="n">
-        <v>0</v>
-      </c>
       <c r="R90" t="n">
         <v>0</v>
       </c>
@@ -16825,9 +16765,6 @@
       <c r="O97" t="n">
         <v>0</v>
       </c>
-      <c r="Q97" t="n">
-        <v>0</v>
-      </c>
       <c r="R97" t="n">
         <v>0</v>
       </c>
@@ -18109,9 +18046,6 @@
       <c r="O105" t="n">
         <v>0</v>
       </c>
-      <c r="Q105" t="n">
-        <v>0</v>
-      </c>
       <c r="R105" t="n">
         <v>0</v>
       </c>
@@ -19245,9 +19179,6 @@
       <c r="O112" t="n">
         <v>0</v>
       </c>
-      <c r="Q112" t="n">
-        <v>0</v>
-      </c>
       <c r="R112" t="n">
         <v>0</v>
       </c>
@@ -20381,9 +20312,6 @@
       <c r="O119" t="n">
         <v>1</v>
       </c>
-      <c r="Q119" t="n">
-        <v>0</v>
-      </c>
       <c r="R119" t="n">
         <v>0.01898885667429354</v>
       </c>
@@ -21665,9 +21593,6 @@
       <c r="O127" t="n">
         <v>2</v>
       </c>
-      <c r="Q127" t="n">
-        <v>0</v>
-      </c>
       <c r="R127" t="n">
         <v>0.03781640513471149</v>
       </c>
@@ -22801,9 +22726,6 @@
       <c r="O134" t="n">
         <v>2</v>
       </c>
-      <c r="Q134" t="n">
-        <v>0</v>
-      </c>
       <c r="R134" t="n">
         <v>0.03781640513471149</v>
       </c>
@@ -23937,9 +23859,6 @@
       <c r="O141" t="n">
         <v>0</v>
       </c>
-      <c r="Q141" t="n">
-        <v>0</v>
-      </c>
       <c r="R141" t="n">
         <v>0</v>
       </c>
@@ -25221,9 +25140,6 @@
       <c r="O149" t="n">
         <v>0</v>
       </c>
-      <c r="Q149" t="n">
-        <v>0</v>
-      </c>
       <c r="R149" t="n">
         <v>0</v>
       </c>
@@ -26357,9 +26273,6 @@
       <c r="O156" t="n">
         <v>0</v>
       </c>
-      <c r="Q156" t="n">
-        <v>0</v>
-      </c>
       <c r="R156" t="n">
         <v>0</v>
       </c>
@@ -27493,9 +27406,6 @@
       <c r="O163" t="n">
         <v>1</v>
       </c>
-      <c r="Q163" t="n">
-        <v>0</v>
-      </c>
       <c r="R163" t="n">
         <v>0.01890820256735574</v>
       </c>
@@ -28777,9 +28687,6 @@
       <c r="O171" t="n">
         <v>1</v>
       </c>
-      <c r="Q171" t="n">
-        <v>0</v>
-      </c>
       <c r="R171" t="n">
         <v>0.01890820256735574</v>
       </c>
@@ -29913,9 +29820,6 @@
       <c r="O178" t="n">
         <v>2</v>
       </c>
-      <c r="Q178" t="n">
-        <v>0</v>
-      </c>
       <c r="R178" t="n">
         <v>0.03781640513471149</v>
       </c>
@@ -31049,9 +30953,6 @@
       <c r="O185" t="n">
         <v>1</v>
       </c>
-      <c r="Q185" t="n">
-        <v>0</v>
-      </c>
       <c r="R185" t="n">
         <v>0.01890820256735574</v>
       </c>
@@ -32333,9 +32234,6 @@
       <c r="O193" t="n">
         <v>0</v>
       </c>
-      <c r="Q193" t="n">
-        <v>0</v>
-      </c>
       <c r="R193" t="n">
         <v>0</v>
       </c>
@@ -33469,9 +33367,6 @@
       <c r="O200" t="n">
         <v>2</v>
       </c>
-      <c r="Q200" t="n">
-        <v>0</v>
-      </c>
       <c r="R200" t="n">
         <v>0.03781640513471149</v>
       </c>
@@ -34605,9 +34500,6 @@
       <c r="O207" t="n">
         <v>0</v>
       </c>
-      <c r="Q207" t="n">
-        <v>0</v>
-      </c>
       <c r="R207" t="n">
         <v>0</v>
       </c>
@@ -35889,9 +35781,6 @@
       <c r="O215" t="n">
         <v>0</v>
       </c>
-      <c r="Q215" t="n">
-        <v>0</v>
-      </c>
       <c r="R215" t="n">
         <v>0</v>
       </c>
@@ -37025,9 +36914,6 @@
       <c r="O222" t="n">
         <v>1</v>
       </c>
-      <c r="Q222" t="n">
-        <v>0</v>
-      </c>
       <c r="R222" t="n">
         <v>0.01882042249213636</v>
       </c>
@@ -38161,9 +38047,6 @@
       <c r="O229" t="n">
         <v>0</v>
       </c>
-      <c r="Q229" t="n">
-        <v>0</v>
-      </c>
       <c r="R229" t="n">
         <v>0</v>
       </c>
@@ -39445,9 +39328,6 @@
       <c r="O237" t="n">
         <v>2</v>
       </c>
-      <c r="Q237" t="n">
-        <v>0</v>
-      </c>
       <c r="R237" t="n">
         <v>0.03764084498427271</v>
       </c>
@@ -40581,9 +40461,6 @@
       <c r="O244" t="n">
         <v>1</v>
       </c>
-      <c r="Q244" t="n">
-        <v>0</v>
-      </c>
       <c r="R244" t="n">
         <v>0.01882042249213636</v>
       </c>
@@ -41865,9 +41742,6 @@
       <c r="O252" t="n">
         <v>0</v>
       </c>
-      <c r="Q252" t="n">
-        <v>0</v>
-      </c>
       <c r="R252" t="n">
         <v>0</v>
       </c>
@@ -43001,9 +42875,6 @@
       <c r="O259" t="n">
         <v>0</v>
       </c>
-      <c r="Q259" t="n">
-        <v>0</v>
-      </c>
       <c r="R259" t="n">
         <v>0</v>
       </c>
@@ -44137,9 +44008,6 @@
       <c r="O266" t="n">
         <v>2</v>
       </c>
-      <c r="Q266" t="n">
-        <v>0</v>
-      </c>
       <c r="R266" t="n">
         <v>0.03764084498427271</v>
       </c>
@@ -45421,9 +45289,6 @@
       <c r="O274" t="n">
         <v>1</v>
       </c>
-      <c r="Q274" t="n">
-        <v>0</v>
-      </c>
       <c r="R274" t="n">
         <v>0.01882042249213636</v>
       </c>
@@ -46557,9 +46422,6 @@
       <c r="O281" t="n">
         <v>0</v>
       </c>
-      <c r="Q281" t="n">
-        <v>0</v>
-      </c>
       <c r="R281" t="n">
         <v>0</v>
       </c>
@@ -47693,9 +47555,6 @@
       <c r="O288" t="n">
         <v>4</v>
       </c>
-      <c r="Q288" t="n">
-        <v>0</v>
-      </c>
       <c r="R288" t="n">
         <v>0.07528168996854542</v>
       </c>
@@ -48977,9 +48836,6 @@
       <c r="O296" t="n">
         <v>0</v>
       </c>
-      <c r="Q296" t="n">
-        <v>0</v>
-      </c>
       <c r="R296" t="n">
         <v>0</v>
       </c>
@@ -50113,9 +49969,6 @@
       <c r="O303" t="n">
         <v>1</v>
       </c>
-      <c r="Q303" t="n">
-        <v>0</v>
-      </c>
       <c r="R303" t="n">
         <v>0.01873060270490507</v>
       </c>
@@ -51397,9 +51250,6 @@
       <c r="O311" t="n">
         <v>0</v>
       </c>
-      <c r="Q311" t="n">
-        <v>0</v>
-      </c>
       <c r="R311" t="n">
         <v>0</v>
       </c>
@@ -52533,9 +52383,6 @@
       <c r="O318" t="n">
         <v>0</v>
       </c>
-      <c r="Q318" t="n">
-        <v>0</v>
-      </c>
       <c r="R318" t="n">
         <v>0</v>
       </c>
@@ -53669,9 +53516,6 @@
       <c r="O325" t="n">
         <v>4</v>
       </c>
-      <c r="Q325" t="n">
-        <v>0</v>
-      </c>
       <c r="R325" t="n">
         <v>0.07492241081962027</v>
       </c>
@@ -54805,9 +54649,6 @@
       <c r="O332" t="n">
         <v>0</v>
       </c>
-      <c r="Q332" t="n">
-        <v>0</v>
-      </c>
       <c r="R332" t="n">
         <v>0</v>
       </c>
@@ -56089,9 +55930,6 @@
       <c r="O340" t="n">
         <v>1</v>
       </c>
-      <c r="Q340" t="n">
-        <v>0</v>
-      </c>
       <c r="R340" t="n">
         <v>0.01873060270490507</v>
       </c>
@@ -57225,9 +57063,6 @@
       <c r="O347" t="n">
         <v>0</v>
       </c>
-      <c r="Q347" t="n">
-        <v>0</v>
-      </c>
       <c r="R347" t="n">
         <v>0</v>
       </c>
@@ -58361,9 +58196,6 @@
       <c r="O354" t="n">
         <v>1</v>
       </c>
-      <c r="Q354" t="n">
-        <v>0</v>
-      </c>
       <c r="R354" t="n">
         <v>0.01873060270490507</v>
       </c>
@@ -59645,9 +59477,6 @@
       <c r="O362" t="n">
         <v>0</v>
       </c>
-      <c r="Q362" t="n">
-        <v>0</v>
-      </c>
       <c r="R362" t="n">
         <v>0</v>
       </c>
@@ -60781,9 +60610,6 @@
       <c r="O369" t="n">
         <v>2</v>
       </c>
-      <c r="Q369" t="n">
-        <v>0</v>
-      </c>
       <c r="R369" t="n">
         <v>0.03746120540981013</v>
       </c>
@@ -62065,9 +61891,6 @@
       <c r="O377" t="n">
         <v>1</v>
       </c>
-      <c r="Q377" t="n">
-        <v>0</v>
-      </c>
       <c r="R377" t="n">
         <v>0.01873060270490507</v>
       </c>
@@ -63200,9 +63023,6 @@
       </c>
       <c r="O384" t="n">
         <v>1</v>
-      </c>
-      <c r="Q384" t="n">
-        <v>0</v>
       </c>
       <c r="R384" t="n">
         <v>0.01873060270490507</v>
